--- a/cleaning_pipeline_R/neotree_scripts/zim-scripts/Bindura Hospital Admission - metadata.xlsx
+++ b/cleaning_pipeline_R/neotree_scripts/zim-scripts/Bindura Hospital Admission - metadata.xlsx
@@ -1668,7 +1668,7 @@
         <v/>
       </c>
       <c r="O19" t="str">
-        <v>($NoPulseOx = false and $SatsAir &lt; 90) or ($NoPulseOx = false and $RR &gt; 60)</v>
+        <v>$SatsAir &lt; 90 or $RR &gt; 60</v>
       </c>
       <c r="P19" t="str">
         <v/>
@@ -2460,7 +2460,7 @@
         <v>BloodSugarmmol</v>
       </c>
       <c r="G31" t="str">
-        <v>Blood Sugar (mmol/L)      (2.5 - 4.5)</v>
+        <v>Blood Sugar (mmol/L)      (2.6 - 8.3)</v>
       </c>
       <c r="H31" t="str">
         <v>number</v>
@@ -2614,13 +2614,13 @@
         <v>No</v>
       </c>
       <c r="M33" t="str">
-        <v>$BloodSugarmmol &lt; 2.6 or $BloodSugarmg &lt; 46.8</v>
+        <v>$BloodSugarmmol &lt; 2.6 or $BloodSugarmg &lt; 47</v>
       </c>
       <c r="N33" t="str">
         <v>[{"value":"true","valueLabel":"Yes"},{"value":"false","valueLabel":"No"}]</v>
       </c>
       <c r="O33" t="str">
-        <v>$BloodSugarmmol &lt; 2.6 or $BloodSugarmg &lt; 46.8</v>
+        <v>$BloodSugarmmol &lt; 2.6 or $BloodSugarmg &lt; 47</v>
       </c>
       <c r="P33" t="str">
         <v/>
@@ -3093,7 +3093,7 @@
         <v/>
       </c>
       <c r="N40" t="str">
-        <v>[{"value":"AD","valueLabel":"Abdominal distension"},{"value":"BBA","valueLabel":"Born Before Arrival"},{"value":"Convulsions","valueLabel":"Convulsions"},{"value":"DIB","valueLabel":"Difficulty in breathing"},{"value":"DU","valueLabel":"Dumped baby"},{"value":"Fev","valueLabel":"Fever"},{"value":"FD","valueLabel":"Not sucking / feeding difficulties"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"NE","valueLabel":"Neonatal encephalopathy"},{"value":"HIVExp","valueLabel":"HIV Exposed"},{"value":"J","valueLabel":"Jaundice"},{"value":"LowBirthWeight","valueLabel":"Low Birth Weight"},{"value":"Apg","valueLabel":"Low Apgars"},{"value":"Mec","valueLabel":"Possible Meconium Aspiration"},{"value":"NTD","valueLabel":"Neural Tube Defect / Spina Bifida"},{"value":"Prem","valueLabel":"Prematurity"},{"value":"PremRDS","valueLabel":"Prematurity with RDS"},{"value":"SPn","valueLabel":"Severe Pneumonia"},{"value":"OM","valueLabel":"Omphalocele"},{"value":"Cong","valueLabel":"Other congenital abnormality"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"Risk","valueLabel":"Risk factors for sepsis"},{"value":"NSep","valueLabel":"Suspected neonatal sepsis"},{"value":"Syph_Exp","valueLabel":"Syphillis Exposure"},{"value":"O","valueLabel":"Other"}]</v>
+        <v>[{"value":"AD","valueLabel":"Abdominal distension"},{"value":"BBA","valueLabel":"Born Before Arrival"},{"value":"Convulsions","valueLabel":"Convulsions"},{"value":"DIB","valueLabel":"Difficulty in breathing"},{"value":"DU","valueLabel":"Dumped baby"},{"value":"Fev","valueLabel":"Fever"},{"value":"FD","valueLabel":"Not sucking / feeding difficulties"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"NE","valueLabel":"Neonatal encephalopathy"},{"value":"HIVExp","valueLabel":"HIV Exposed"},{"value":"J","valueLabel":"Jaundice"},{"value":"LowBirthWeight","valueLabel":"Low Birth Weight"},{"value":"Apg","valueLabel":"Low Apgars"},{"value":"Mec","valueLabel":"Possible Meconium Aspiration"},{"value":"NTD","valueLabel":"Neural Tube Defect / Spina Bifida"},{"value":"Prem","valueLabel":"Premature"},{"value":"PremRDS","valueLabel":"Prematurity with RDS"},{"value":"SPn","valueLabel":"Severe Pneumonia"},{"value":"OM","valueLabel":"Omphalocele"},{"value":"Cong","valueLabel":"Other congenital abnormality"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"Risk","valueLabel":"Risk factors for sepsis"},{"value":"NSep","valueLabel":"Sepsis suspected"},{"value":"Syph_Exp","valueLabel":"Syphillis Exposure"},{"value":"O","valueLabel":"Other"}]</v>
       </c>
       <c r="O40" t="str">
         <v/>
@@ -3229,7 +3229,7 @@
         <v/>
       </c>
       <c r="N42" t="str">
-        <v>[{"value":"Cong","valueLabel":"Other Congenital Abnormality","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AD","valueLabel":"Abdominal distension","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Conv","valueLabel":"Convulsions","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DU","valueLabel":"Dumped baby","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Fev","valueLabel":"Fever","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DF","valueLabel":"Difficulty Feeding","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GSchis","valueLabel":"Gastroschisis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIE","valueLabel":"Hypoxic ischaemic encephalopathy","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIVX","valueLabel":"HIV Exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"J","valueLabel":"Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LBW","valueLabel":"Low birth weight","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mec","valueLabel":"Possible Meconium aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NTD","valueLabel":"Neural tube defect / spina bifida","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OM","valueLabel":"Omphalocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Prematurity","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pneum","valueLabel":"Pneumonia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RDS","valueLabel":"Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Syph_Exp","valueLabel":"Syphilis exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
+        <v>[{"value":"Cong","valueLabel":"Other Congenital Abnormality","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AD","valueLabel":"Abdominal distension","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Conv","valueLabel":"Convulsions","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DU","valueLabel":"Dumped baby","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Fev","valueLabel":"Fever","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DF","valueLabel":"Difficulty Feeding","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GSchis","valueLabel":"Gastroschisis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIE","valueLabel":"Hypoxic ischaemic encephalopathy","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIVX","valueLabel":"HIV Exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"J","valueLabel":"Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LBW","valueLabel":"Low birth weight","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mec","valueLabel":"Possible Meconium aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NTD","valueLabel":"Neural tube defect / spina bifida","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OM","valueLabel":"Omphalocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Premature","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pneum","valueLabel":"Pneumonia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RDS","valueLabel":"Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Syph_Exp","valueLabel":"Syphilis exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O42" t="str">
         <v/>
@@ -3362,7 +3362,7 @@
         <v>No</v>
       </c>
       <c r="M44" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N44" t="str">
         <v/>
@@ -3430,7 +3430,7 @@
         <v>No</v>
       </c>
       <c r="M45" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N45" t="str">
         <v/>
@@ -3634,7 +3634,7 @@
         <v>No</v>
       </c>
       <c r="M48" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N48" t="str">
         <v/>
@@ -4228,7 +4228,7 @@
         <v>Gestation</v>
       </c>
       <c r="G57" t="str">
-        <v>Gestational age at birth (weeks.days)</v>
+        <v>Estimated Gestational age at birth (weeks.days)</v>
       </c>
       <c r="H57" t="str">
         <v>number</v>
@@ -4252,7 +4252,7 @@
         <v/>
       </c>
       <c r="O57" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P57" t="str">
         <v/>
@@ -4320,7 +4320,7 @@
         <v>[{"value":"LMP","valueLabel":"Last Menstrual Period (LMP)"},{"value":"FH","valueLabel":"Fundal height"},{"value":"USS","valueLabel":"USS"}]</v>
       </c>
       <c r="O58" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P58" t="str">
         <v/>
@@ -4388,7 +4388,7 @@
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O59" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P59" t="str">
         <v/>
@@ -4456,7 +4456,7 @@
         <v/>
       </c>
       <c r="O60" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P60" t="str">
         <v/>
@@ -4524,7 +4524,7 @@
         <v/>
       </c>
       <c r="O61" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P61" t="str">
         <v/>
@@ -4592,7 +4592,7 @@
         <v/>
       </c>
       <c r="O62" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P62" t="str">
         <v/>
@@ -4654,13 +4654,13 @@
         <v>No</v>
       </c>
       <c r="M63" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N63" t="str">
         <v>[{"value":"Stim","valueLabel":"Stimulation","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Suc","valueLabel":"Suctioning","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O2","valueLabel":"Oxygen","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BVM","valueLabel":"Bag Valve Mask Ventilation (BVM)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CPR","valueLabel":"Cardio Pulmonary Resuscitation (CPR)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O63" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P63" t="str">
         <v/>
@@ -7581,7 +7581,7 @@
         <v>$FeverSR = true</v>
       </c>
       <c r="N106" t="str">
-        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 -3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"more than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 -3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"more than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O106" t="str">
         <v>$FeverSR = true</v>
@@ -7717,7 +7717,7 @@
         <v>$RespSR != 'Norm'</v>
       </c>
       <c r="N108" t="str">
-        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 -3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 -3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O108" t="str">
         <v>$RespSR != 'Norm'</v>
@@ -7853,7 +7853,7 @@
         <v>$Vomiting != 'Norm'</v>
       </c>
       <c r="N110" t="str">
-        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 - 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 - 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O110" t="str">
         <v>$Vomiting != 'Norm'</v>
@@ -8193,7 +8193,7 @@
         <v>$Age &gt; 47.9 or $AgeEstimate = 'INF72' or $AgeEstimate = 'INF'</v>
       </c>
       <c r="N115" t="str">
-        <v>[{"value":"Norm","valueLabel":"Passing urine normally"},{"value":"NoPU","valueLabel":"Not passing urine"}]</v>
+        <v>[{"value":"Norm","valueLabel":"Passing urine normally"},{"value":"NPU","valueLabel":"Not passing urine"}]</v>
       </c>
       <c r="O115" t="str">
         <v/>
@@ -8329,7 +8329,7 @@
         <v>$SRNeuroOther != 'Norm'</v>
       </c>
       <c r="N117" t="str">
-        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 - 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 - 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O117" t="str">
         <v>$SRNeuroOther != 'Norm'</v>
@@ -9006,13 +9006,13 @@
         <v>No</v>
       </c>
       <c r="M127" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N127" t="str">
         <v>[{"value":"true","valueLabel":"Yes"},{"value":"false","valueLabel":"No"}]</v>
       </c>
       <c r="O127" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P127" t="str">
         <v/>
@@ -9216,7 +9216,7 @@
         <v>[{"value":"HA","valueLabel":"Harare"},{"value":"BU","valueLabel":"Bulawayo"},{"value":"MC","valueLabel":"Mashonaland Central"},{"value":"ME","valueLabel":"Mashonaland East"},{"value":"MW","valueLabel":"Mashonaland West"},{"value":"MA","valueLabel":"Manicaland"},{"value":"MAS","valueLabel":"Masvingo"},{"value":"MN","valueLabel":"Matabeleland North"},{"value":"MS","valueLabel":"Matabeleland South"},{"value":"MID","valueLabel":"Midlands"}]</v>
       </c>
       <c r="O130" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P130" t="str">
         <v/>
@@ -9284,7 +9284,7 @@
         <v/>
       </c>
       <c r="O131" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P131" t="str">
         <v/>
@@ -9352,7 +9352,7 @@
         <v/>
       </c>
       <c r="O132" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P132" t="str">
         <v/>
@@ -9420,7 +9420,7 @@
         <v/>
       </c>
       <c r="O133" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P133" t="str">
         <v/>
@@ -9488,7 +9488,7 @@
         <v/>
       </c>
       <c r="O134" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P134" t="str">
         <v/>
@@ -9556,7 +9556,7 @@
         <v/>
       </c>
       <c r="O135" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P135" t="str">
         <v/>
@@ -9624,7 +9624,7 @@
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"}]</v>
       </c>
       <c r="O136" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P136" t="str">
         <v/>
@@ -9692,7 +9692,7 @@
         <v/>
       </c>
       <c r="O137" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P137" t="str">
         <v/>
@@ -9760,7 +9760,7 @@
         <v/>
       </c>
       <c r="O138" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P138" t="str">
         <v/>
@@ -9822,13 +9822,13 @@
         <v>No</v>
       </c>
       <c r="M139" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N139" t="str">
         <v>[{"value":"MAR","valueLabel":"Married","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DIV","valueLabel":"Divorced","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"WID","valueLabel":"Widowed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"S","valueLabel":"Single","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O139" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P139" t="str">
         <v/>
@@ -9893,10 +9893,10 @@
         <v/>
       </c>
       <c r="N140" t="str">
-        <v>[{"value":"A","valueLabel":"African"},{"value":"AA","valueLabel":"AfricanAmerican"},{"value":"AS","valueLabel":"Asian/Pacific Islander"},{"value":"W","valueLabel":"White"},{"value":"NA","valueLabel":"NativeAmerican"},{"value":"O","valueLabel":"Other"}]</v>
+        <v>[{"value":"A","valueLabel":"African"},{"value":"AS","valueLabel":"Asian/Pacific Islander"},{"value":"W","valueLabel":"White"},{"value":"NA","valueLabel":"NativeAmerican"},{"value":"O","valueLabel":"Other"}]</v>
       </c>
       <c r="O140" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P140" t="str">
         <v/>
@@ -9964,7 +9964,7 @@
         <v/>
       </c>
       <c r="O141" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P141" t="str">
         <v/>
@@ -10026,13 +10026,13 @@
         <v>No</v>
       </c>
       <c r="M142" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N142" t="str">
         <v>[{"value":"AP","valueLabel":"Apostolic (Christian Protestant)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RC","valueLabel":"Roman Catholic (Christian)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PE","valueLabel":"Pentecostal (Christian Protestant)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"A","valueLabel":"Anglican (Christian Protestant)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MD","valueLabel":"Methodist","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Ba","valueLabel":"Baptist (Christian Protestant)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"P","valueLabel":"Prespyterian (Christian Protestant)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SDA","valueLabel":"Seventh Day Adventist (SDA) (Christian Protestant)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CP","valueLabel":"Other Christian Protestant","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"J","valueLabel":"Jewish","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"JW","valueLabel":"Jehova's Witness","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MU","valueLabel":"Muslim","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AG","valueLabel":"Agnostic","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ATH","valueLabel":"Atheist","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Z","valueLabel":"Zion","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O142" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P142" t="str">
         <v/>
@@ -10162,13 +10162,13 @@
         <v>No</v>
       </c>
       <c r="M144" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N144" t="str">
         <v>[{"value":"true","valueLabel":"Yes"},{"value":"false","valueLabel":"No"}]</v>
       </c>
       <c r="O144" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P144" t="str">
         <v/>
@@ -10295,7 +10295,7 @@
         <v>Yes</v>
       </c>
       <c r="L146" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="M146" t="str">
         <v/>
@@ -10437,7 +10437,7 @@
         <v/>
       </c>
       <c r="N148" t="str">
-        <v>[{"value":"R","valueLabel":"Positive"},{"value":"NR","valueLabel":"Negative"},{"value":"U","valueLabel":"Unknown"}]</v>
+        <v>[{"value":"R","valueLabel":"Positive"},{"value":"U","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O148" t="str">
         <v>$MatHIVtest = true</v>
@@ -10549,10 +10549,10 @@
         <v>form</v>
       </c>
       <c r="F150" t="str">
-        <v>HAART</v>
+        <v>MaHAART</v>
       </c>
       <c r="G150" t="str">
-        <v>Maternal HAART Status</v>
+        <v>Is the mother on HAART?</v>
       </c>
       <c r="H150" t="str">
         <v>dropdown</v>
@@ -10620,7 +10620,7 @@
         <v>LengthHAART</v>
       </c>
       <c r="G151" t="str">
-        <v>Mother on HAART since when?</v>
+        <v>Maternal HAART Initiation</v>
       </c>
       <c r="H151" t="str">
         <v>dropdown</v>
@@ -10638,7 +10638,7 @@
         <v>No</v>
       </c>
       <c r="M151" t="str">
-        <v>$HAART = 'Y'</v>
+        <v>$MaHAART = 'Y'</v>
       </c>
       <c r="N151" t="str">
         <v>[{"value":"1stTrim","valueLabel":"1st Trimester or earlier"},{"value":"2ndTrim","valueLabel":"2nd Trimester"},{"value":"3rdTrim","valueLabel":"3rd Trimester more than 1 month before delivery"},{"value":"Late","valueLabel":"Less than 1 month before delivery"},{"value":"U","valueLabel":"Unknown"}]</v>
@@ -10706,7 +10706,7 @@
         <v>No</v>
       </c>
       <c r="M152" t="str">
-        <v>$HAART= 'Y'</v>
+        <v>$MaHAART = 'Y'</v>
       </c>
       <c r="N152" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"NA","valueLabel":"Not applicable"}]</v>
@@ -10756,7 +10756,7 @@
         <v>VLNumber</v>
       </c>
       <c r="G153" t="str">
-        <v>Viral Load</v>
+        <v>Viral Load (copies/ml)</v>
       </c>
       <c r="H153" t="str">
         <v>number</v>
@@ -10978,13 +10978,13 @@
         <v>No</v>
       </c>
       <c r="M156" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N156" t="str">
         <v>[{"value":"Y","valueLabel":"Yes","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"N","valueLabel":"No","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"U","valueLabel":"Not sure","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O156" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P156" t="str">
         <v/>
@@ -11522,13 +11522,13 @@
         <v>No</v>
       </c>
       <c r="M164" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N164" t="str">
         <v>[{"value":"An","valueLabel":"Anaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DM","valueLabel":"Diabetes","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HD","valueLabel":"Heart disease","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HTN","valueLabel":"Hypertension or pre-eclampsia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MAL","valueLabel":"Malaria","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"STD","valueLabel":"Sexually Transmitted Disease (other than HIV/syphilis)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"THY","valueLabel":"Thyroid disease / goitre","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TU","valueLabel":"Tuberculosis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"U","valueLabel":"Unknown","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O164" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P164" t="str">
         <v/>
@@ -11800,7 +11800,7 @@
         <v/>
       </c>
       <c r="O168" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P168" t="str">
         <v/>
@@ -11868,7 +11868,7 @@
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O169" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P169" t="str">
         <v/>
@@ -11936,7 +11936,7 @@
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O170" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P170" t="str">
         <v/>
@@ -12004,7 +12004,7 @@
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O171" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P171" t="str">
         <v/>
@@ -12066,13 +12066,13 @@
         <v>No</v>
       </c>
       <c r="M172" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N172" t="str">
         <v>[{"value":"IPT0","valueLabel":"No SP doses","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IPT1","valueLabel":"1 SP dose","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IPT2","valueLabel":"2 SP doses","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IPT3","valueLabel":"3 SP doses","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IPT4","valueLabel":"4 SP doses","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IPT5+","valueLabel":"5 or more SP doses","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IPTU","valueLabel":"Not sure","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O172" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P172" t="str">
         <v/>
@@ -12134,13 +12134,13 @@
         <v>No</v>
       </c>
       <c r="M173" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N173" t="str">
         <v>[{"value":"Y","valueLabel":"Yes","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"N","valueLabel":"No","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"U","valueLabel":"Not Sure","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O173" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P173" t="str">
         <v/>
@@ -12202,13 +12202,13 @@
         <v>No</v>
       </c>
       <c r="M174" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N174" t="str">
         <v>[{"value":"SVB","valueLabel":"Significant Vaginal Bleeding","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pre","valueLabel":"Pre-eclampsia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Conv","valueLabel":"Convulsions / Eclampsia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Poly","valueLabel":"Polyhydramnios","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Olig","valueLabel":"Oligohydramnios","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O174" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P174" t="str">
         <v/>
@@ -12684,7 +12684,7 @@
         <v>[{"value":"NOPROM","valueLabel":"less than 18 hours"},{"value":"PROM","valueLabel":"greater than 18 hours"}]</v>
       </c>
       <c r="O181" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P181" t="str">
         <v/>
@@ -12746,13 +12746,13 @@
         <v>No</v>
       </c>
       <c r="M182" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N182" t="str">
-        <v>[{"value":"PROM","valueLabel":"PROM more than 18 hrs","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MF","valueLabel":"Maternal fever in labour","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OL","valueLabel":"Offensive Liquor","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pr2nd","valueLabel":"Prolonged second stage","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival (BBA)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Prematurity &lt; 37 weeks","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
+        <v>[{"value":"PROM","valueLabel":"PROM more than 18 hrs","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MF","valueLabel":"Maternal fever in labour","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OL","valueLabel":"Offensive Liquor","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pr2nd","valueLabel":"Prolonged second stage labour","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival (BBA)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Prematurity &lt; 37 weeks","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O182" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P182" t="str">
         <v/>
@@ -12820,7 +12820,7 @@
         <v>[{"value":"Vertex","valueLabel":"Vertex"},{"value":"Brow","valueLabel":"Brow"},{"value":"Breech","valueLabel":"Breech"},{"value":"Face","valueLabel":"Face"},{"value":"Unk","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O183" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P183" t="str">
         <v/>
@@ -12888,7 +12888,7 @@
         <v>[{"value":"1","valueLabel":"Spontaneous Vaginal Delivery"},{"value":"7","valueLabel":"Induced Vaginal Delivery"},{"value":"6","valueLabel":"Breech extraction (vaginal)"},{"value":"2","valueLabel":"Vacuum extraction"},{"value":"3","valueLabel":"Forceps extraction"},{"value":"4","valueLabel":"Elective Ceasarian Section (ELCS)"},{"value":"5","valueLabel":"Emergency Ceasarian Section (EMCS)"}]</v>
       </c>
       <c r="O184" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P184" t="str">
         <v/>
@@ -13092,7 +13092,7 @@
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"NS","valueLabel":"Not Sure"}]</v>
       </c>
       <c r="O187" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P187" t="str">
         <v/>
@@ -13160,7 +13160,7 @@
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"NS","valueLabel":"Not Sure"}]</v>
       </c>
       <c r="O188" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P188" t="str">
         <v/>
@@ -13973,7 +13973,7 @@
         <v/>
       </c>
       <c r="N200" t="str">
-        <v>[{"value":"An","valueLabel":"Anaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BI","valueLabel":"Birth Trauma","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Cong","valueLabel":"Congenital Abnormality","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CHD","valueLabel":"Consider Congenital Heart Disease","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Conv","valueLabel":"Convulsions","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Dhyd","valueLabel":"Dehydration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DF","valueLabel":"Difficulty Feeding","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DUM","valueLabel":"Abandoned baby","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIVExp","valueLabel":"HIV Exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIVU","valueLabel":"HIV Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Syph_Exp","valueLabel":"Syphilis exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HypogAs","valueLabel":"Hypoglycaemia (NOT symptomatic)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HypogSy","valueLabel":"Hypoglycaemia (symptomatic)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RiHypog","valueLabel":"Risk of hypoglycaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BA","valueLabel":"Hypoxic Ischaemic Encephalopathy","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GSchis","valueLabel":"Gastroschisis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MJ","valueLabel":"Physiological Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LBW","valueLabel":"Low Birth Weight (1500-2499g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"VLBW","valueLabel":"Very Low Birth Weight (1000-1499g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ExLBW","valueLabel":"Extremely low birth weight (&lt;1000g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MA","valueLabel":"Possible Meconium Aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MecEx","valueLabel":"Meconium exposure (asymptomatic baby)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MiHypo","valueLabel":"Mild Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ModHypo","valueLabel":"Moderate Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SHypo","valueLabel":"Severe Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Hyperth","valueLabel":"Hyperthermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NSep","valueLabel":"Suspected neonatal sepsis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Risk","valueLabel":"Risk factors for sepsis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NB","valueLabel":"Normal Baby","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"PN","valueLabel":"Pneumonia /  Bronchiolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Premature (32 to 37 weeks)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"VPrem","valueLabel":"Very Premature (28-31+6 weeks)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ExPrem","valueLabel":"Extremely Premature (&lt;28 weeks)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PremRD","valueLabel":"Premature baby with Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Safe","valueLabel":"Safekeeping","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TermRD","valueLabel":"Term with Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DJ","valueLabel":"Pathological Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"sHIE","valueLabel":"Suspected Hypoxic Ischaemic Encephalopathy (HIE)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ProJ","valueLabel":"Prolonged Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CleftLip","valueLabel":"Cleft lip","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CleftRD","valueLabel":"Cleft lip and/or palate with RD","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CleftPal","valueLabel":"Cleft palate","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Omph","valueLabel":"Omphalocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Myelo","valueLabel":"Myelomeningocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CDH","valueLabel":"Congenital dislocation of the hip (CDH)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MiTalipes","valueLabel":"Mild Talipes (club foot)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MoTalipes","valueLabel":"Moderate Talipes (club foot)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NecEnt","valueLabel":"Consider Necrotising Enterocolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"An","valueLabel":"Anaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born before arrival","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BT","valueLabel":"Birth injury / Trauma","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Cong","valueLabel":"Congenital Abnormality","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CHD","valueLabel":"Consider Congenital Heart Disease","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Conv","valueLabel":"Convulsions","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Dhyd","valueLabel":"Dehydration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DF","valueLabel":"Difficulty Feeding","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DUM","valueLabel":"Abandoned baby","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIVExp","valueLabel":"HIV Exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIVU","valueLabel":"HIV Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Syph_Exp","valueLabel":"Syphilis exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HypogAs","valueLabel":"Hypoglycaemia (NOT symptomatic)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HypogSy","valueLabel":"Hypoglycaemia (symptomatic)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RiHypog","valueLabel":"Risk of hypoglycaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BA","valueLabel":"Hypoxic Ischaemic Encephalopathy","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GSchis","valueLabel":"Gastroschisis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MJ","valueLabel":"Physiological Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LBW","valueLabel":"Low Birth Weight (1500-2499g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"VLBW","valueLabel":"Very Low Birth Weight (1000-1499g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ExLBW","valueLabel":"Extremely low birth weight (&lt;1000g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MA","valueLabel":"Possible Meconium Aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MecEx","valueLabel":"Meconium exposure (asymptomatic baby)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MiHypo","valueLabel":"Mild Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ModHypo","valueLabel":"Moderate Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SHypo","valueLabel":"Severe Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Hyperth","valueLabel":"Hyperthermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NSep","valueLabel":"Suspected neonatal sepsis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Risk","valueLabel":"Risk factors for sepsis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NB","valueLabel":"Normal Baby","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"PN","valueLabel":"Pneumonia /  Bronchiolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Premature (32 to 37 weeks)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"VPrem","valueLabel":"Very Premature (28-31+6 weeks)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ExPrem","valueLabel":"Extremely Premature (&lt;28 weeks)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PremRD","valueLabel":"Premature baby with Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Safe","valueLabel":"Safekeeping","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TermRD","valueLabel":"Term with Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DJ","valueLabel":"Pathological Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"sHIE","valueLabel":"Suspected Hypoxic Ischaemic Encephalopathy (HIE)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ProJ","valueLabel":"Prolonged Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CleftLip","valueLabel":"Cleft lip","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CleftRD","valueLabel":"Cleft lip and/or palate with RD","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CleftPal","valueLabel":"Cleft palate","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Omph","valueLabel":"Omphalocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Myelo","valueLabel":"Myelomeningocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CDH","valueLabel":"Congenital dislocation of the hip (CDH)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MiTalipes","valueLabel":"Mild Talipes (club foot)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MoTalipes","valueLabel":"Moderate Talipes (club foot)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NecEnt","valueLabel":"Consider Necrotising Enterocolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O200" t="str">
         <v/>
@@ -14044,7 +14044,7 @@
         <v/>
       </c>
       <c r="O201" t="str">
-        <v>($DangerSigns = 'Grun' or $RR &gt; 60 or $SatsO2 &lt; 90 or $WOB = 'Mod' or $WOB = 'Sev' or $Diagnoses = 'RDN' or $AdmReason = 'PREMRDS') and $NobCPAP = false</v>
+        <v xml:space="preserve">($DangerSigns = 'Grun' or $RR &gt; 60 or $SatsO2 &lt; 90 or $WOB = 'Mod' or $WOB = 'Sev' or $AdmReason = 'PREMRDS') </v>
       </c>
       <c r="P201" t="str">
         <v/>
@@ -15412,7 +15412,7 @@
         <v>Bindura Provincial Hospital</v>
       </c>
       <c r="C3" t="str">
-        <v>Born Before Arrival</v>
+        <v>Born before arrival</v>
       </c>
       <c r="D3" t="str">
         <v>Born before arrival</v>
@@ -15424,7 +15424,7 @@
         <v>e3cb5ede-7fc1-43aa-8d79-bd36a4cd332e</v>
       </c>
       <c r="G3" t="str">
-        <v>Born Before Arrival</v>
+        <v>Born before arrival</v>
       </c>
       <c r="H3" t="str">
         <v>7101</v>
@@ -15469,7 +15469,7 @@
         <v>BBA</v>
       </c>
       <c r="V3" t="str">
-        <v>Born Before Arrival</v>
+        <v>Born before arrival</v>
       </c>
       <c r="W3" t="str">
         <v/>
@@ -15489,19 +15489,19 @@
         <v>Bindura Provincial Hospital</v>
       </c>
       <c r="C4" t="str">
-        <v>Birth Trauma</v>
+        <v>Birth injury / Trauma</v>
       </c>
       <c r="D4" t="str">
         <v>Birth Trauma</v>
       </c>
       <c r="E4" t="str">
-        <v>BI</v>
+        <v>BT</v>
       </c>
       <c r="F4" t="str">
         <v>ec2adc2a-3fa6-438d-89de-7e3b87f568c6</v>
       </c>
       <c r="G4" t="str">
-        <v>Birth Trauma</v>
+        <v>Birth injury / Trauma</v>
       </c>
       <c r="H4" t="str">
         <v>7102</v>
@@ -15543,10 +15543,10 @@
         <v>diagnosis</v>
       </c>
       <c r="U4" t="str">
-        <v>BI</v>
+        <v>BT</v>
       </c>
       <c r="V4" t="str">
-        <v>Birth Trauma</v>
+        <v>Birth injury / Trauma</v>
       </c>
       <c r="W4" t="str">
         <v/>
@@ -17857,7 +17857,7 @@
         <v>Bindura Provincial Hospital</v>
       </c>
       <c r="C31" t="str">
-        <v>? Congenital Pneumonia</v>
+        <v>Congenital Pneumonia</v>
       </c>
       <c r="D31" t="str">
         <v>RDN - Congenital Pneumonia</v>
@@ -17869,7 +17869,7 @@
         <v>2f74e32f-d1a8-4a5a-b672-cee9b6d6fd38</v>
       </c>
       <c r="G31" t="str">
-        <v>? Congenital Pneumonia</v>
+        <v>Congenital Pneumonia</v>
       </c>
       <c r="H31" t="str">
         <v>7129</v>
@@ -17931,7 +17931,7 @@
         <v>CongPneu</v>
       </c>
       <c r="V31" t="str">
-        <v>? Congenital Pneumonia</v>
+        <v>Congenital Pneumonia</v>
       </c>
       <c r="W31" t="str">
         <v/>
